--- a/input/detect_DV_BUY_20190729.xlsx
+++ b/input/detect_DV_BUY_20190729.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B877056C-FD2C-4B39-8CFE-89C2229C583B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD10022-FB80-4269-890B-53486DCADDD4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9012" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
   <si>
     <t>A股代码</t>
   </si>
@@ -319,6 +319,139 @@
   </si>
   <si>
     <t>20240910</t>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>伟星股份</t>
+  </si>
+  <si>
+    <t>国光股份</t>
+  </si>
+  <si>
+    <t>富安娜</t>
+  </si>
+  <si>
+    <t>冀中能源</t>
+  </si>
+  <si>
+    <t>广汇能源</t>
+  </si>
+  <si>
+    <t>华阳股份</t>
+  </si>
+  <si>
+    <t>潞安环能</t>
+  </si>
+  <si>
+    <t>山西焦煤</t>
+  </si>
+  <si>
+    <t>济川药业</t>
+  </si>
+  <si>
+    <t>伟隆股份</t>
+  </si>
+  <si>
+    <t>通化东宝</t>
+  </si>
+  <si>
+    <t>欧普照明</t>
+  </si>
+  <si>
+    <t>新华保险</t>
+  </si>
+  <si>
+    <t>工业富联</t>
+  </si>
+  <si>
+    <t>格力电器</t>
+  </si>
+  <si>
+    <t>大华股份</t>
+  </si>
+  <si>
+    <t>生益科技</t>
+  </si>
+  <si>
+    <t>地素时尚</t>
+  </si>
+  <si>
+    <t>新 和 成</t>
+  </si>
+  <si>
+    <t>健帆生物</t>
+  </si>
+  <si>
+    <t>华新水泥</t>
+  </si>
+  <si>
+    <t>上峰水泥</t>
+  </si>
+  <si>
+    <t>利尔化学</t>
+  </si>
+  <si>
+    <t>英科医疗</t>
+  </si>
+  <si>
+    <t>金域医学</t>
+  </si>
+  <si>
+    <t>旗滨集团</t>
+  </si>
+  <si>
+    <t>北大荒</t>
+  </si>
+  <si>
+    <t>基蛋生物</t>
+  </si>
+  <si>
+    <t>振德医疗</t>
+  </si>
+  <si>
+    <t>天华新能</t>
+  </si>
+  <si>
+    <t>三全食品</t>
+  </si>
+  <si>
+    <t>通威股份</t>
+  </si>
+  <si>
+    <t>桃李面包</t>
+  </si>
+  <si>
+    <t>浙江美大</t>
+  </si>
+  <si>
+    <t>罗莱生活</t>
+  </si>
+  <si>
+    <t>新宝股份</t>
+  </si>
+  <si>
+    <t>鲁阳节能</t>
+  </si>
+  <si>
+    <t>重庆啤酒</t>
+  </si>
+  <si>
+    <t>汤臣倍健</t>
+  </si>
+  <si>
+    <t>广信股份</t>
+  </si>
+  <si>
+    <t>特变电工</t>
+  </si>
+  <si>
+    <t>永兴材料</t>
+  </si>
+  <si>
+    <t>山煤国际</t>
   </si>
 </sst>
 </file>
@@ -737,21 +870,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B20A7AC-FD1C-4DB7-BA1B-5DFB9B322B5E}">
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -768,45 +901,48 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>0.3</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="6">
+      <c r="N1" s="6">
         <v>5000000</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <f>COUNTA(A2:A300)</f>
         <v>43</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>85</v>
       </c>
-      <c r="Q1" s="6">
-        <f>M1/O1</f>
+      <c r="R1" s="6">
+        <f>N1/P1</f>
         <v>116279.06976744186</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -822,23 +958,26 @@
       <c r="E2" s="2">
         <v>35.07</v>
       </c>
-      <c r="F2">
-        <f>$I$1-E2*($I$1-$K$1)/100</f>
+      <c r="F2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2">
+        <f>$J$1-E2*($J$1-$L$1)/100</f>
         <v>1.5336700000000001</v>
       </c>
-      <c r="G2" s="7">
-        <f>F2*$Q$1</f>
+      <c r="H2" s="7">
+        <f>G2*$R$1</f>
         <v>178333.72093023258</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="7">
-        <f>SUM(G2:G300)</f>
+      <c r="L2" s="7">
+        <f>SUM(H2:H300)</f>
         <v>7920541.8604651187</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -854,16 +993,19 @@
       <c r="E3" s="2">
         <v>24.04</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F39" si="0">$I$1-E3*($I$1-$K$1)/100</f>
+      <c r="F3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G39" si="0">$J$1-E3*($J$1-$L$1)/100</f>
         <v>1.7432400000000001</v>
       </c>
-      <c r="G3" s="7">
-        <f t="shared" ref="G3:G39" si="1">F3*$Q$1</f>
+      <c r="H3" s="7">
+        <f t="shared" ref="H3:H39" si="1">G3*$R$1</f>
         <v>202702.32558139536</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -879,16 +1021,19 @@
       <c r="E4" s="2">
         <v>28.14</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4">
         <f t="shared" si="0"/>
         <v>1.66534</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="7">
         <f t="shared" si="1"/>
         <v>193644.18604651163</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -904,16 +1049,19 @@
       <c r="E5" s="2">
         <v>29.33</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>1.6427300000000002</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H5" s="7">
         <f t="shared" si="1"/>
         <v>191015.1162790698</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -929,16 +1077,19 @@
       <c r="E6" s="2">
         <v>27.09</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>1.6852900000000002</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="7">
         <f t="shared" si="1"/>
         <v>195963.95348837212</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -954,16 +1105,19 @@
       <c r="E7" s="2">
         <v>16.64</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7">
         <f t="shared" si="0"/>
         <v>1.8838400000000002</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="7">
         <f t="shared" si="1"/>
         <v>219051.16279069771</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>64</v>
       </c>
@@ -979,16 +1133,19 @@
       <c r="E8" s="2">
         <v>17.71</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8">
         <f t="shared" si="0"/>
         <v>1.8635100000000002</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="7">
         <f t="shared" si="1"/>
         <v>216687.20930232562</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1004,16 +1161,19 @@
       <c r="E9" s="2">
         <v>35.89</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9">
         <f t="shared" si="0"/>
         <v>1.5180900000000002</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="7">
         <f t="shared" si="1"/>
         <v>176522.09302325585</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1029,16 +1189,19 @@
       <c r="E10" s="2">
         <v>99.59</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>0.30778999999999979</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="7">
         <f t="shared" si="1"/>
         <v>35789.534883720909</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1054,16 +1217,19 @@
       <c r="E11" s="2">
         <v>94.8</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11">
         <f t="shared" si="0"/>
         <v>0.39880000000000004</v>
       </c>
-      <c r="G11" s="7">
+      <c r="H11" s="7">
         <f t="shared" si="1"/>
         <v>46372.093023255817</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1079,16 +1245,19 @@
       <c r="E12" s="2">
         <v>52.8</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12">
         <f t="shared" si="0"/>
         <v>1.1968000000000001</v>
       </c>
-      <c r="G12" s="7">
+      <c r="H12" s="7">
         <f t="shared" si="1"/>
         <v>139162.79069767444</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -1104,16 +1273,19 @@
       <c r="E13" s="2">
         <v>22.12</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13">
         <f t="shared" si="0"/>
         <v>1.7797200000000002</v>
       </c>
-      <c r="G13" s="7">
+      <c r="H13" s="7">
         <f t="shared" si="1"/>
         <v>206944.18604651166</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -1129,16 +1301,19 @@
       <c r="E14" s="2">
         <v>8.93</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>2.0303300000000002</v>
       </c>
-      <c r="G14" s="7">
+      <c r="H14" s="7">
         <f t="shared" si="1"/>
         <v>236084.88372093026</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1154,16 +1329,19 @@
       <c r="E15" s="2">
         <v>5.22</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15">
         <f t="shared" si="0"/>
         <v>2.1008200000000001</v>
       </c>
-      <c r="G15" s="7">
+      <c r="H15" s="7">
         <f t="shared" si="1"/>
         <v>244281.39534883722</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1179,16 +1357,19 @@
       <c r="E16" s="2">
         <v>3.98</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16">
         <f t="shared" si="0"/>
         <v>2.1243800000000004</v>
       </c>
-      <c r="G16" s="7">
+      <c r="H16" s="7">
         <f t="shared" si="1"/>
         <v>247020.9302325582</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -1204,16 +1385,19 @@
       <c r="E17" s="2">
         <v>2.0499999999999998</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17">
         <f t="shared" si="0"/>
         <v>2.1610500000000004</v>
       </c>
-      <c r="G17" s="7">
+      <c r="H17" s="7">
         <f t="shared" si="1"/>
         <v>251284.88372093029</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>91</v>
       </c>
@@ -1229,16 +1413,19 @@
       <c r="E18" s="2">
         <v>0.41</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18">
         <f t="shared" si="0"/>
         <v>2.1922100000000002</v>
       </c>
-      <c r="G18" s="7">
+      <c r="H18" s="7">
         <f t="shared" si="1"/>
         <v>254908.13953488375</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -1254,16 +1441,19 @@
       <c r="E19" s="2">
         <v>1.37</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19">
         <f t="shared" si="0"/>
         <v>2.1739700000000002</v>
       </c>
-      <c r="G19" s="7">
+      <c r="H19" s="7">
         <f t="shared" si="1"/>
         <v>252787.20930232562</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1279,16 +1469,19 @@
       <c r="E20" s="2">
         <v>25.69</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20">
         <f t="shared" si="0"/>
         <v>1.7118900000000001</v>
       </c>
-      <c r="G20" s="7">
+      <c r="H20" s="7">
         <f t="shared" si="1"/>
         <v>199056.97674418607</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1304,16 +1497,19 @@
       <c r="E21" s="2">
         <v>25.69</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="0"/>
         <v>1.7118900000000001</v>
       </c>
-      <c r="G21" s="7">
+      <c r="H21" s="7">
         <f t="shared" si="1"/>
         <v>199056.97674418607</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1329,16 +1525,19 @@
       <c r="E22" s="2">
         <v>23.46</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22">
         <f t="shared" si="0"/>
         <v>1.7542600000000002</v>
       </c>
-      <c r="G22" s="7">
+      <c r="H22" s="7">
         <f t="shared" si="1"/>
         <v>203983.72093023258</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1354,16 +1553,19 @@
       <c r="E23" s="2">
         <v>14.7</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23">
         <f t="shared" si="0"/>
         <v>1.9207000000000001</v>
       </c>
-      <c r="G23" s="7">
+      <c r="H23" s="7">
         <f t="shared" si="1"/>
         <v>223337.20930232559</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1379,16 +1581,19 @@
       <c r="E24" s="2">
         <v>13.7</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24">
         <f t="shared" si="0"/>
         <v>1.9397000000000002</v>
       </c>
-      <c r="G24" s="7">
+      <c r="H24" s="7">
         <f t="shared" si="1"/>
         <v>225546.51162790699</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1404,16 +1609,19 @@
       <c r="E25" s="2">
         <v>20.27</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25">
         <f t="shared" si="0"/>
         <v>1.8148700000000002</v>
       </c>
-      <c r="G25" s="7">
+      <c r="H25" s="7">
         <f t="shared" si="1"/>
         <v>211031.39534883725</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -1429,16 +1637,19 @@
       <c r="E26" s="2">
         <v>11.66</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26">
         <f t="shared" si="0"/>
         <v>1.9784600000000001</v>
       </c>
-      <c r="G26" s="7">
+      <c r="H26" s="7">
         <f t="shared" si="1"/>
         <v>230053.48837209304</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -1454,16 +1665,19 @@
       <c r="E27" s="2">
         <v>1.23</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27">
         <f t="shared" si="0"/>
         <v>2.1766300000000003</v>
       </c>
-      <c r="G27" s="7">
+      <c r="H27" s="7">
         <f t="shared" si="1"/>
         <v>253096.51162790702</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>93</v>
       </c>
@@ -1479,16 +1693,19 @@
       <c r="E28" s="2">
         <v>4.1100000000000003</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G28">
         <f t="shared" si="0"/>
         <v>2.1219100000000002</v>
       </c>
-      <c r="G28" s="7">
+      <c r="H28" s="7">
         <f t="shared" si="1"/>
         <v>246733.72093023258</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1504,16 +1721,19 @@
       <c r="E29" s="2">
         <v>62.45</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29">
         <f t="shared" si="0"/>
         <v>1.01345</v>
       </c>
-      <c r="G29" s="7">
+      <c r="H29" s="7">
         <f t="shared" si="1"/>
         <v>117843.02325581395</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1529,16 +1749,19 @@
       <c r="E30" s="2">
         <v>58.98</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30">
         <f t="shared" si="0"/>
         <v>1.0793800000000002</v>
       </c>
-      <c r="G30" s="7">
+      <c r="H30" s="7">
         <f t="shared" si="1"/>
         <v>125509.30232558142</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1554,16 +1777,19 @@
       <c r="E31" s="2">
         <v>56.95</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31">
         <f t="shared" si="0"/>
         <v>1.11795</v>
       </c>
-      <c r="G31" s="7">
+      <c r="H31" s="7">
         <f t="shared" si="1"/>
         <v>129994.18604651163</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1579,16 +1805,19 @@
       <c r="E32" s="2">
         <v>69.19</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32">
         <f t="shared" si="0"/>
         <v>0.88539000000000012</v>
       </c>
-      <c r="G32" s="7">
+      <c r="H32" s="7">
         <f t="shared" si="1"/>
         <v>102952.32558139536</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -1604,16 +1833,19 @@
       <c r="E33" s="2">
         <v>53.16</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33">
         <f t="shared" si="0"/>
         <v>1.1899600000000001</v>
       </c>
-      <c r="G33" s="7">
+      <c r="H33" s="7">
         <f t="shared" si="1"/>
         <v>138367.44186046513</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -1629,16 +1861,19 @@
       <c r="E34" s="2">
         <v>53.16</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G34">
         <f t="shared" si="0"/>
         <v>1.1899600000000001</v>
       </c>
-      <c r="G34" s="7">
+      <c r="H34" s="7">
         <f t="shared" si="1"/>
         <v>138367.44186046513</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -1654,16 +1889,19 @@
       <c r="E35" s="2">
         <v>36.86</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35">
         <f t="shared" si="0"/>
         <v>1.49966</v>
       </c>
-      <c r="G35" s="7">
+      <c r="H35" s="7">
         <f t="shared" si="1"/>
         <v>174379.06976744186</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -1679,16 +1917,19 @@
       <c r="E36" s="2">
         <v>45.13</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36">
         <f t="shared" si="0"/>
         <v>1.34253</v>
       </c>
-      <c r="G36" s="7">
+      <c r="H36" s="7">
         <f t="shared" si="1"/>
         <v>156108.13953488372</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -1704,16 +1945,19 @@
       <c r="E37" s="2">
         <v>44.57</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37">
         <f t="shared" si="0"/>
         <v>1.35317</v>
       </c>
-      <c r="G37" s="7">
+      <c r="H37" s="7">
         <f t="shared" si="1"/>
         <v>157345.34883720931</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -1729,16 +1973,19 @@
       <c r="E38" s="2">
         <v>45.13</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38">
         <f t="shared" si="0"/>
         <v>1.34253</v>
       </c>
-      <c r="G38" s="7">
+      <c r="H38" s="7">
         <f t="shared" si="1"/>
         <v>156108.13953488372</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1754,16 +2001,19 @@
       <c r="E39" s="2">
         <v>10.59</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G39">
         <f t="shared" si="0"/>
         <v>1.9987900000000001</v>
       </c>
-      <c r="G39" s="7">
+      <c r="H39" s="7">
         <f t="shared" si="1"/>
         <v>232417.44186046513</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>95</v>
       </c>
@@ -1779,16 +2029,19 @@
       <c r="E40" s="2">
         <v>11.55</v>
       </c>
-      <c r="F40">
-        <f t="shared" ref="F40:F44" si="2">$I$1-E40*($I$1-$K$1)/100</f>
+      <c r="F40" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G40">
+        <f t="shared" ref="G40:G44" si="2">$J$1-E40*($J$1-$L$1)/100</f>
         <v>1.98055</v>
       </c>
-      <c r="G40" s="7">
-        <f t="shared" ref="G40:G44" si="3">F40*$Q$1</f>
+      <c r="H40" s="7">
+        <f t="shared" ref="H40:H44" si="3">G40*$R$1</f>
         <v>230296.51162790699</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -1804,16 +2057,19 @@
       <c r="E41" s="2">
         <v>11.03</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41">
         <f t="shared" si="2"/>
         <v>1.9904300000000001</v>
       </c>
-      <c r="G41" s="7">
+      <c r="H41" s="7">
         <f t="shared" si="3"/>
         <v>231445.34883720931</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1829,16 +2085,19 @@
       <c r="E42" s="2">
         <v>11.98</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42">
         <f t="shared" si="2"/>
         <v>1.9723800000000002</v>
       </c>
-      <c r="G42" s="7">
+      <c r="H42" s="7">
         <f t="shared" si="3"/>
         <v>229346.51162790702</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -1854,16 +2113,19 @@
       <c r="E43" s="2">
         <v>79.37</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43">
         <f t="shared" si="2"/>
         <v>0.69196999999999997</v>
       </c>
-      <c r="G43" s="7">
+      <c r="H43" s="7">
         <f t="shared" si="3"/>
         <v>80461.627906976748</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -1879,47 +2141,61 @@
       <c r="E44" s="2">
         <v>98.07</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G44">
         <f t="shared" si="2"/>
         <v>0.33667000000000025</v>
       </c>
-      <c r="G44" s="7">
+      <c r="H44" s="7">
         <f t="shared" si="3"/>
         <v>39147.674418604678</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G47" s="7"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G48" s="7"/>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G49" s="7"/>
-    </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G50" s="7"/>
-    </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G51" s="7"/>
-    </row>
-    <row r="52" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G52" s="7"/>
-    </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G53" s="7"/>
-    </row>
-    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G54" s="7"/>
-    </row>
-    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G55" s="7"/>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F45" s="7"/>
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F46" s="7"/>
+      <c r="H46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F47" s="7"/>
+      <c r="H47" s="7"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F48" s="7"/>
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F49" s="7"/>
+      <c r="H49" s="7"/>
+    </row>
+    <row r="50" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F50" s="7"/>
+      <c r="H50" s="7"/>
+    </row>
+    <row r="51" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F51" s="7"/>
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F52" s="7"/>
+      <c r="H52" s="7"/>
+    </row>
+    <row r="53" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F53" s="7"/>
+      <c r="H53" s="7"/>
+    </row>
+    <row r="54" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F54" s="7"/>
+      <c r="H54" s="7"/>
+    </row>
+    <row r="55" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F55" s="7"/>
+      <c r="H55" s="7"/>
     </row>
   </sheetData>
   <sortState ref="A2:E39">
